--- a/fix-target-codes-and-display/ig/FRHealthProfessionalLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRHealthProfessionalLMCDAFHIR.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:53:12+00:00</t>
+    <t>2026-08-20T15:08:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/FRHealthProfessionalLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRHealthProfessionalLMCDAFHIR.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T15:08:45+00:00</t>
+    <t>2026-08-20T15:24:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/FRHealthProfessionalLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRHealthProfessionalLMCDAFHIR.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T15:24:46+00:00</t>
+    <t>2026-08-21T08:13:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/FRHealthProfessionalLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRHealthProfessionalLMCDAFHIR.xlsx
@@ -10,12 +10,15 @@
     <sheet name="Mapping Table 0" r:id="rId4" sheetId="2"/>
     <sheet name="Mapping Table 1" r:id="rId5" sheetId="3"/>
     <sheet name="Mapping Table 2" r:id="rId6" sheetId="4"/>
+    <sheet name="Mapping Table 3" r:id="rId7" sheetId="5"/>
+    <sheet name="Mapping Table 4" r:id="rId8" sheetId="6"/>
+    <sheet name="Mapping Table 5" r:id="rId9" sheetId="7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="80">
   <si>
     <t>Property</t>
   </si>
@@ -38,6 +41,9 @@
     <t>Name</t>
   </si>
   <si>
+    <t>FRHealthProfessionalLMCDAFHIR</t>
+  </si>
+  <si>
     <t>Title</t>
   </si>
   <si>
@@ -53,10 +59,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T08:13:05+00:00</t>
+    <t>2026-08-23T21:45:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -132,58 +141,79 @@
     <t>AssignedEntity.id</t>
   </si>
   <si>
+    <t>FRLMHealthProfessional.address</t>
+  </si>
+  <si>
+    <t>AssignedEntity.addr</t>
+  </si>
+  <si>
+    <t>FRLMHealthProfessional.telecom</t>
+  </si>
+  <si>
+    <t>AssignedEntity.telecom</t>
+  </si>
+  <si>
+    <t>FRLMHealthProfessional.professionalRole.role</t>
+  </si>
+  <si>
+    <t>AssignedEntity.code</t>
+  </si>
+  <si>
+    <t>FRLMHealthProfessional.professionalRole.organisation</t>
+  </si>
+  <si>
+    <t>AssignedEntity.representedOrganization</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-assigned-person|0.1.0</t>
+  </si>
+  <si>
     <t>FRLMHealthProfessional.name</t>
   </si>
   <si>
-    <t>AssignedEntity.assignedPerson.name</t>
-  </si>
-  <si>
-    <t>FRLMHealthProfessional.name.family</t>
-  </si>
-  <si>
-    <t>AssignedEntity.assignedPerson.name.family</t>
-  </si>
-  <si>
-    <t>FRLMHealthProfessional.name.given</t>
-  </si>
-  <si>
-    <t>AssignedEntity.assignedPerson.name.given</t>
-  </si>
-  <si>
-    <t>FRLMHealthProfessional.name.prefix</t>
-  </si>
-  <si>
-    <t>AssignedEntity.assignedPerson.name.prefix</t>
-  </si>
-  <si>
-    <t>FRLMHealthProfessional.name.suffix</t>
-  </si>
-  <si>
-    <t>AssignedEntity.assignedPerson.name.suffix</t>
-  </si>
-  <si>
-    <t>FRLMHealthProfessional.address</t>
-  </si>
-  <si>
-    <t>AssignedEntity.addr</t>
-  </si>
-  <si>
-    <t>FRLMHealthProfessional.telecom</t>
-  </si>
-  <si>
-    <t>AssignedEntity.telecom</t>
-  </si>
-  <si>
-    <t>FRLMHealthProfessional.professionalRole.role</t>
-  </si>
-  <si>
-    <t>AssignedEntity.code</t>
-  </si>
-  <si>
-    <t>FRLMHealthProfessional.professionalRole.organisation</t>
-  </si>
-  <si>
-    <t>AssignedEntity.representedOrganization</t>
+    <t>Person.name</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMHumanName|0.1.0</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-name|0.1.0</t>
+  </si>
+  <si>
+    <t>FRLMHumanName.use</t>
+  </si>
+  <si>
+    <t>PN.use</t>
+  </si>
+  <si>
+    <t>FRLMHumanName.family</t>
+  </si>
+  <si>
+    <t>PN.item.family</t>
+  </si>
+  <si>
+    <t>FRLMHumanName.given</t>
+  </si>
+  <si>
+    <t>PN.item.given</t>
+  </si>
+  <si>
+    <t>FRLMHumanName.prefix</t>
+  </si>
+  <si>
+    <t>PN.item.prefix</t>
+  </si>
+  <si>
+    <t>FRLMHumanName.suffix</t>
+  </si>
+  <si>
+    <t>PN.item.suffix</t>
+  </si>
+  <si>
+    <t>FRLMHumanName.period</t>
+  </si>
+  <si>
+    <t>PN.validTime</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-practitionerRole-document|0.1.0</t>
@@ -216,6 +246,12 @@
     <t>Practitioner.name</t>
   </si>
   <si>
+    <t>Practitioner.address</t>
+  </si>
+  <si>
+    <t>Practitioner.telecom</t>
+  </si>
+  <si>
     <t>Practitioner.name.family</t>
   </si>
   <si>
@@ -226,12 +262,6 @@
   </si>
   <si>
     <t>Practitioner.name.suffix</t>
-  </si>
-  <si>
-    <t>Practitioner.address</t>
-  </si>
-  <si>
-    <t>Practitioner.telecom</t>
   </si>
 </sst>
 </file>
@@ -400,79 +430,83 @@
       <c r="A4" t="s" s="2">
         <v>6</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" t="s" s="2">
+        <v>7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
@@ -483,187 +517,122 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E8" s="2"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D10" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D11" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D12" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D13" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="E13" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -672,94 +641,55 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E3" s="2"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D4" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D5" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D6" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="E6" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -768,79 +698,297 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E8" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s" s="2">
         <v>64</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="E6" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>73</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -850,10 +998,10 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E6" s="2"/>
     </row>
@@ -863,64 +1011,108 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="E7" s="2"/>
     </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D8" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D10" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D11" t="s" s="2">
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="E11" s="2"/>
+      <c r="E2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E6" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/fix-target-codes-and-display/ig/FRHealthProfessionalLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRHealthProfessionalLMCDAFHIR.xlsx
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-23T21:45:18+00:00</t>
+    <t>2026-08-24T13:13:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/FRHealthProfessionalLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRHealthProfessionalLMCDAFHIR.xlsx
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-24T13:13:01+00:00</t>
+    <t>2026-08-25T11:34:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/FRHealthProfessionalLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRHealthProfessionalLMCDAFHIR.xlsx
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T11:34:21+00:00</t>
+    <t>2026-08-25T11:56:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/FRHealthProfessionalLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRHealthProfessionalLMCDAFHIR.xlsx
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T11:56:50+00:00</t>
+    <t>2026-08-25T20:08:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/FRHealthProfessionalLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRHealthProfessionalLMCDAFHIR.xlsx
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T20:08:46+00:00</t>
+    <t>2026-08-31T08:09:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
